--- a/deliverables/benchmark/benchmark.xlsx
+++ b/deliverables/benchmark/benchmark.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R72709a5c28174ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="2" r:id="R32c3fc64aa254afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="3" r:id="R675ab332d61446bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbbe9db14a5ff420f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="2" r:id="R4386ad4c396144cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="3" r:id="R477fb98c20744fff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,8 +41,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF172B3A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -57,6 +63,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF315B7D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF4F8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -156,7 +167,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -203,6 +214,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -757,9 +776,45 @@
       <x:c r="E18" s="26"/>
       <x:c r="F18" s="27"/>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="15" t="str">
+        <x:v>Evidence boundary</x:v>
+      </x:c>
+      <x:c r="B20" s="15"/>
+      <x:c r="C20" s="15"/>
+      <x:c r="D20" s="15"/>
+      <x:c r="E20" s="15"/>
+      <x:c r="F20" s="15"/>
+      <x:c r="G20" s="15"/>
+      <x:c r="H20" s="15"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="31" t="str">
+        <x:v>This workbook documents a synthetic, safety-redacted dataset. It is not a performance report for the deployed LLaVA tuned-v3 detector; current live-system evidence is recorded under deliverables/runtime_validation/.</x:v>
+      </x:c>
+      <x:c r="B21" s="31"/>
+      <x:c r="C21" s="31"/>
+      <x:c r="D21" s="31"/>
+      <x:c r="E21" s="31"/>
+      <x:c r="F21" s="31"/>
+      <x:c r="G21" s="31"/>
+      <x:c r="H21" s="31"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="31"/>
+      <x:c r="B22" s="31"/>
+      <x:c r="C22" s="31"/>
+      <x:c r="D22" s="31"/>
+      <x:c r="E22" s="31"/>
+      <x:c r="F22" s="31"/>
+      <x:c r="G22" s="31"/>
+      <x:c r="H22" s="31"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A20:H20"/>
+    <x:mergeCell ref="A21:H22"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B7:B7">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="PASS"/>
@@ -872,7 +927,7 @@
         <x:v>image_sha256</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="44" customHeight="1">
+    <x:row r="2" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
         <x:v>aegis-v1-001-benign</x:v>
       </x:c>
@@ -942,7 +997,7 @@
       </x:c>
       <x:c r="X2" s="9" t="str"/>
     </x:row>
-    <x:row r="3" ht="44" customHeight="1">
+    <x:row r="3" ht="66" hidden="0" customHeight="1">
       <x:c r="A3" s="9" t="str">
         <x:v>aegis-v1-001-malicious</x:v>
       </x:c>
@@ -1012,7 +1067,7 @@
       </x:c>
       <x:c r="X3" s="9" t="str"/>
     </x:row>
-    <x:row r="4" ht="44" customHeight="1">
+    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A4" s="9" t="str">
         <x:v>aegis-v1-002-benign</x:v>
       </x:c>
@@ -1082,7 +1137,7 @@
       </x:c>
       <x:c r="X4" s="9" t="str"/>
     </x:row>
-    <x:row r="5" ht="44" customHeight="1">
+    <x:row r="5" ht="66" hidden="0" customHeight="1">
       <x:c r="A5" s="9" t="str">
         <x:v>aegis-v1-002-malicious</x:v>
       </x:c>
@@ -1152,7 +1207,7 @@
       </x:c>
       <x:c r="X5" s="9" t="str"/>
     </x:row>
-    <x:row r="6" ht="44" customHeight="1">
+    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>aegis-v1-003-benign</x:v>
       </x:c>
@@ -1226,7 +1281,7 @@
         <x:v>7070cf54fd2114045d2069ef1d4b51063b912d31d2edb606e889425417f2953d</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="44" customHeight="1">
+    <x:row r="7" ht="66" hidden="0" customHeight="1">
       <x:c r="A7" s="9" t="str">
         <x:v>aegis-v1-003-malicious</x:v>
       </x:c>
@@ -1300,7 +1355,7 @@
         <x:v>c1d5bd6d9fbfe7ceb64bb5b9e1f61071ffe1f3d6c3c73a5e19a5c35a71180db4</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="44" customHeight="1">
+    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>aegis-v1-004-benign</x:v>
       </x:c>
@@ -1374,7 +1429,7 @@
         <x:v>ec57853c3ac9aec2e523dcd94d4bd237f58db91ccd863f3e0f95a0bff18f37cf</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="44" customHeight="1">
+    <x:row r="9" ht="66" hidden="0" customHeight="1">
       <x:c r="A9" s="9" t="str">
         <x:v>aegis-v1-004-malicious</x:v>
       </x:c>
@@ -1448,7 +1503,7 @@
         <x:v>c2cf76c063170a15f1bc7a4d7c0e7b7944cdfe6fb212b96e27096190bb6fc6e0</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="44" customHeight="1">
+    <x:row r="10" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>aegis-v1-005-benign</x:v>
       </x:c>
@@ -1518,7 +1573,7 @@
       </x:c>
       <x:c r="X10" s="9" t="str"/>
     </x:row>
-    <x:row r="11" ht="44" customHeight="1">
+    <x:row r="11" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>aegis-v1-005-malicious</x:v>
       </x:c>
@@ -1588,7 +1643,7 @@
       </x:c>
       <x:c r="X11" s="9" t="str"/>
     </x:row>
-    <x:row r="12" ht="44" customHeight="1">
+    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A12" s="9" t="str">
         <x:v>aegis-v1-006-benign</x:v>
       </x:c>
@@ -1658,7 +1713,7 @@
       </x:c>
       <x:c r="X12" s="9" t="str"/>
     </x:row>
-    <x:row r="13" ht="44" customHeight="1">
+    <x:row r="13" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A13" s="9" t="str">
         <x:v>aegis-v1-006-malicious</x:v>
       </x:c>
@@ -1728,7 +1783,7 @@
       </x:c>
       <x:c r="X13" s="9" t="str"/>
     </x:row>
-    <x:row r="14" ht="44" customHeight="1">
+    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A14" s="9" t="str">
         <x:v>aegis-v1-007-benign</x:v>
       </x:c>
@@ -1802,7 +1857,7 @@
         <x:v>e93a389e8b3e79cc21605b3a6bc6d3f59b7515d23cd7a226a3b171761368d3ba</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="44" customHeight="1">
+    <x:row r="15" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A15" s="9" t="str">
         <x:v>aegis-v1-007-malicious</x:v>
       </x:c>
@@ -1876,7 +1931,7 @@
         <x:v>2e9ca0f7d690ec1590705ff85141506b3b1aea089c2af1433202a2dbb85f056e</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="44" customHeight="1">
+    <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A16" s="9" t="str">
         <x:v>aegis-v1-008-benign</x:v>
       </x:c>
@@ -1950,7 +2005,7 @@
         <x:v>fb0b40db6f35a98b67a53faefc5654b61643f367be66a9ae271124a07a313d05</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="44" customHeight="1">
+    <x:row r="17" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A17" s="9" t="str">
         <x:v>aegis-v1-008-malicious</x:v>
       </x:c>
@@ -2024,7 +2079,7 @@
         <x:v>25621df382900df2aa295a144936d74c55c10f83eb7dc9221672f14c1a87f0a9</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="44" customHeight="1">
+    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" s="9" t="str">
         <x:v>aegis-v1-009-benign</x:v>
       </x:c>
@@ -2094,7 +2149,7 @@
       </x:c>
       <x:c r="X18" s="9" t="str"/>
     </x:row>
-    <x:row r="19" ht="44" customHeight="1">
+    <x:row r="19" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A19" s="9" t="str">
         <x:v>aegis-v1-009-malicious</x:v>
       </x:c>
@@ -2164,7 +2219,7 @@
       </x:c>
       <x:c r="X19" s="9" t="str"/>
     </x:row>
-    <x:row r="20" ht="44" customHeight="1">
+    <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A20" s="9" t="str">
         <x:v>aegis-v1-010-benign</x:v>
       </x:c>
@@ -2234,7 +2289,7 @@
       </x:c>
       <x:c r="X20" s="9" t="str"/>
     </x:row>
-    <x:row r="21" ht="44" customHeight="1">
+    <x:row r="21" ht="66" hidden="0" customHeight="1">
       <x:c r="A21" s="9" t="str">
         <x:v>aegis-v1-010-malicious</x:v>
       </x:c>
@@ -2304,7 +2359,7 @@
       </x:c>
       <x:c r="X21" s="9" t="str"/>
     </x:row>
-    <x:row r="22" ht="44" customHeight="1">
+    <x:row r="22" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A22" s="9" t="str">
         <x:v>aegis-v1-011-benign</x:v>
       </x:c>
@@ -2378,7 +2433,7 @@
         <x:v>b1e97ad7f9c5c9856281560f199b90b8083f532cd0ea43d2886632a538773b17</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="44" customHeight="1">
+    <x:row r="23" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A23" s="9" t="str">
         <x:v>aegis-v1-011-malicious</x:v>
       </x:c>
@@ -2452,7 +2507,7 @@
         <x:v>0a56e4a61265c5a8c38b2e99340bd85e0b0126f21a8df28e227584c86f39d37f</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="44" customHeight="1">
+    <x:row r="24" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A24" s="9" t="str">
         <x:v>aegis-v1-012-benign</x:v>
       </x:c>
@@ -2526,7 +2581,7 @@
         <x:v>4674a1dd5a8a1c4f8097cd8c691a05ee776ecc8a878f74b716398fdd8ef7f861</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="44" customHeight="1">
+    <x:row r="25" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A25" s="9" t="str">
         <x:v>aegis-v1-012-malicious</x:v>
       </x:c>
@@ -2600,7 +2655,7 @@
         <x:v>37db7b1d1219e8bd5291ac1c14a747cd598a6dd7321c5f84330761ef21998693</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="44" customHeight="1">
+    <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A26" s="9" t="str">
         <x:v>aegis-v1-013-benign</x:v>
       </x:c>
@@ -2670,7 +2725,7 @@
       </x:c>
       <x:c r="X26" s="9" t="str"/>
     </x:row>
-    <x:row r="27" ht="44" customHeight="1">
+    <x:row r="27" ht="66" hidden="0" customHeight="1">
       <x:c r="A27" s="9" t="str">
         <x:v>aegis-v1-013-malicious</x:v>
       </x:c>
@@ -2740,7 +2795,7 @@
       </x:c>
       <x:c r="X27" s="9" t="str"/>
     </x:row>
-    <x:row r="28" ht="44" customHeight="1">
+    <x:row r="28" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A28" s="9" t="str">
         <x:v>aegis-v1-014-benign</x:v>
       </x:c>
@@ -2810,7 +2865,7 @@
       </x:c>
       <x:c r="X28" s="9" t="str"/>
     </x:row>
-    <x:row r="29" ht="44" customHeight="1">
+    <x:row r="29" ht="66" hidden="0" customHeight="1">
       <x:c r="A29" s="9" t="str">
         <x:v>aegis-v1-014-malicious</x:v>
       </x:c>
@@ -2880,7 +2935,7 @@
       </x:c>
       <x:c r="X29" s="9" t="str"/>
     </x:row>
-    <x:row r="30" ht="44" customHeight="1">
+    <x:row r="30" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A30" s="9" t="str">
         <x:v>aegis-v1-015-benign</x:v>
       </x:c>
@@ -2954,7 +3009,7 @@
         <x:v>59ca0481c2fde240439d7df60511e5df487ababebe8d313c959879480d41e837</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="44" customHeight="1">
+    <x:row r="31" ht="66" hidden="0" customHeight="1">
       <x:c r="A31" s="9" t="str">
         <x:v>aegis-v1-015-malicious</x:v>
       </x:c>
@@ -3028,7 +3083,7 @@
         <x:v>2029256120fde8e15b24aed83ffa8227b5d8db32115e62ac6fa7acdd3350e600</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="44" customHeight="1">
+    <x:row r="32" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A32" s="9" t="str">
         <x:v>aegis-v1-016-benign</x:v>
       </x:c>
@@ -3102,7 +3157,7 @@
         <x:v>af32f7176fbcbe10195ba9523df0fc785bac8fa868154bd83b20bac21190cfcb</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="44" customHeight="1">
+    <x:row r="33" ht="66" hidden="0" customHeight="1">
       <x:c r="A33" s="9" t="str">
         <x:v>aegis-v1-016-malicious</x:v>
       </x:c>
@@ -3176,7 +3231,7 @@
         <x:v>11990f29aeef54f9444df008d7bf7f5885a67993178559e80581b38751b4df85</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="44" customHeight="1">
+    <x:row r="34" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A34" s="9" t="str">
         <x:v>aegis-v1-017-benign</x:v>
       </x:c>
@@ -3250,7 +3305,7 @@
         <x:v>3ed8245ccfbfb8cb651a0070cf08d4d41018146a9b962a0040530bbbb26beab4</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="44" customHeight="1">
+    <x:row r="35" ht="66" hidden="0" customHeight="1">
       <x:c r="A35" s="9" t="str">
         <x:v>aegis-v1-017-malicious</x:v>
       </x:c>
@@ -3324,7 +3379,7 @@
         <x:v>d09a777dabd0d319b4a608ed018fef971d4d26d90c635fd726b0a4e5824d0589</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="44" customHeight="1">
+    <x:row r="36" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A36" s="9" t="str">
         <x:v>aegis-v1-018-benign</x:v>
       </x:c>
@@ -3398,7 +3453,7 @@
         <x:v>731e37c9164ce118e5908ba4e3570322fe4dd1845ca8d53c7bc41e2f57665a26</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="44" customHeight="1">
+    <x:row r="37" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A37" s="9" t="str">
         <x:v>aegis-v1-018-malicious</x:v>
       </x:c>
@@ -3472,7 +3527,7 @@
         <x:v>bf2ea48569fd794d0a9eb1d94e72bff5f45ba247be7e0dc596aae3c4def04a52</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="44" customHeight="1">
+    <x:row r="38" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A38" s="9" t="str">
         <x:v>aegis-v1-019-benign</x:v>
       </x:c>
@@ -3546,7 +3601,7 @@
         <x:v>00391666a8d0371695547eb1adf3444004cc27a29bb627d4b44a83a0c78e4d8b</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="44" customHeight="1">
+    <x:row r="39" ht="66" hidden="0" customHeight="1">
       <x:c r="A39" s="9" t="str">
         <x:v>aegis-v1-019-malicious</x:v>
       </x:c>
@@ -3620,7 +3675,7 @@
         <x:v>f7d53d36d8a94f1bdc7a2e3b19fabe2d3bd3e0c106332a20dd6a49dc0489e362</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="44" customHeight="1">
+    <x:row r="40" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A40" s="9" t="str">
         <x:v>aegis-v1-020-benign</x:v>
       </x:c>
@@ -3694,7 +3749,7 @@
         <x:v>f314e95cc74c0b327a12bf1dfa72515ea83ffc67eb390fa120ded97ff0f27786</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="44" customHeight="1">
+    <x:row r="41" ht="66" hidden="0" customHeight="1">
       <x:c r="A41" s="9" t="str">
         <x:v>aegis-v1-020-malicious</x:v>
       </x:c>
@@ -3768,7 +3823,7 @@
         <x:v>5fefe7fe156dea1f4ebb759d881a7b4d9fa7486c8577686d94930e508609ed0d</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="44" customHeight="1">
+    <x:row r="42" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A42" s="9" t="str">
         <x:v>aegis-v1-021-benign</x:v>
       </x:c>
@@ -3842,7 +3897,7 @@
         <x:v>8451024825a9920dcab2e7277c126aba3ddef0c069912bef34f912977efddd65</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="44" customHeight="1">
+    <x:row r="43" ht="66" hidden="0" customHeight="1">
       <x:c r="A43" s="9" t="str">
         <x:v>aegis-v1-021-malicious</x:v>
       </x:c>
@@ -3916,7 +3971,7 @@
         <x:v>8451024825a9920dcab2e7277c126aba3ddef0c069912bef34f912977efddd65</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="44" customHeight="1">
+    <x:row r="44" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A44" s="9" t="str">
         <x:v>aegis-v1-022-benign</x:v>
       </x:c>
@@ -3990,7 +4045,7 @@
         <x:v>60224eae3094baab9649992f4696f274200d03c618ef4fefd40a447247a28aac</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="44" customHeight="1">
+    <x:row r="45" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A45" s="9" t="str">
         <x:v>aegis-v1-022-malicious</x:v>
       </x:c>
@@ -4064,7 +4119,7 @@
         <x:v>60224eae3094baab9649992f4696f274200d03c618ef4fefd40a447247a28aac</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="44" customHeight="1">
+    <x:row r="46" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A46" s="9" t="str">
         <x:v>aegis-v1-023-benign</x:v>
       </x:c>
@@ -4138,7 +4193,7 @@
         <x:v>450c9938f63314b0e6249065ac4e32114098204bbb27d3a49395ea482f6cd0a8</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="44" customHeight="1">
+    <x:row r="47" ht="66" hidden="0" customHeight="1">
       <x:c r="A47" s="9" t="str">
         <x:v>aegis-v1-023-malicious</x:v>
       </x:c>
@@ -4212,7 +4267,7 @@
         <x:v>450c9938f63314b0e6249065ac4e32114098204bbb27d3a49395ea482f6cd0a8</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="44" customHeight="1">
+    <x:row r="48" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A48" s="9" t="str">
         <x:v>aegis-v1-024-benign</x:v>
       </x:c>
@@ -4286,7 +4341,7 @@
         <x:v>6eaf9b7b8e679ae218f67c6ddb8638407aa96bd23a193f6d629234c5ddc205a0</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="44" customHeight="1">
+    <x:row r="49" ht="66" hidden="0" customHeight="1">
       <x:c r="A49" s="9" t="str">
         <x:v>aegis-v1-024-malicious</x:v>
       </x:c>
@@ -4360,7 +4415,7 @@
         <x:v>6eaf9b7b8e679ae218f67c6ddb8638407aa96bd23a193f6d629234c5ddc205a0</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="44" customHeight="1">
+    <x:row r="50" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A50" s="9" t="str">
         <x:v>aegis-v1-025-benign</x:v>
       </x:c>
@@ -4434,7 +4489,7 @@
         <x:v>5063450fa76e5d4e1e2989c611d6512ebe113214cf493309c206a6af01833b58</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="44" customHeight="1">
+    <x:row r="51" ht="66" hidden="0" customHeight="1">
       <x:c r="A51" s="9" t="str">
         <x:v>aegis-v1-025-malicious</x:v>
       </x:c>
@@ -4508,7 +4563,7 @@
         <x:v>e32719df87c883a21a498780c64226615af67707c827e4c4ecdc07ebf30b8f63</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="44" customHeight="1">
+    <x:row r="52" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A52" s="9" t="str">
         <x:v>aegis-v1-026-benign</x:v>
       </x:c>
@@ -4582,7 +4637,7 @@
         <x:v>a3effcd88470bc327d6aab5a97e1fa4460245684cdd02685cf57adc0711004c2</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="44" customHeight="1">
+    <x:row r="53" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A53" s="9" t="str">
         <x:v>aegis-v1-026-malicious</x:v>
       </x:c>
@@ -4656,7 +4711,7 @@
         <x:v>1ba1357e970b69456a3b2d925f1b05f946498c6c9955ecd8ce97b45e73c20292</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="44" customHeight="1">
+    <x:row r="54" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A54" s="9" t="str">
         <x:v>aegis-v1-027-benign</x:v>
       </x:c>
@@ -4730,7 +4785,7 @@
         <x:v>c412d825c9f9636db230dd8c039a6e9e28fd6040b5ae78b4635b1f6171814532</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="44" customHeight="1">
+    <x:row r="55" ht="66" hidden="0" customHeight="1">
       <x:c r="A55" s="9" t="str">
         <x:v>aegis-v1-027-malicious</x:v>
       </x:c>
@@ -4804,7 +4859,7 @@
         <x:v>058054a5dfc86417efbc818632912156ce0ebd4b8ecdb00756bbc4fe82ba31f5</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="44" customHeight="1">
+    <x:row r="56" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A56" s="9" t="str">
         <x:v>aegis-v1-028-benign</x:v>
       </x:c>
@@ -4878,7 +4933,7 @@
         <x:v>1f64c17c390837e24fa41a4c676e7637cbdedc0bd506914dbb958121de3251f8</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="44" customHeight="1">
+    <x:row r="57" ht="66" hidden="0" customHeight="1">
       <x:c r="A57" s="9" t="str">
         <x:v>aegis-v1-028-malicious</x:v>
       </x:c>
@@ -4952,7 +5007,7 @@
         <x:v>b5436be1e8c3b5b39fc17d8e8a021a921dac3e33abf026c51d16985b9bc820a4</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="44" customHeight="1">
+    <x:row r="58" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A58" s="9" t="str">
         <x:v>aegis-v1-029-benign</x:v>
       </x:c>
@@ -5022,7 +5077,7 @@
       </x:c>
       <x:c r="X58" s="9" t="str"/>
     </x:row>
-    <x:row r="59" ht="44" customHeight="1">
+    <x:row r="59" ht="66" hidden="0" customHeight="1">
       <x:c r="A59" s="9" t="str">
         <x:v>aegis-v1-029-malicious</x:v>
       </x:c>
@@ -5092,7 +5147,7 @@
       </x:c>
       <x:c r="X59" s="9" t="str"/>
     </x:row>
-    <x:row r="60" ht="44" customHeight="1">
+    <x:row r="60" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A60" s="9" t="str">
         <x:v>aegis-v1-030-benign</x:v>
       </x:c>
@@ -5162,7 +5217,7 @@
       </x:c>
       <x:c r="X60" s="9" t="str"/>
     </x:row>
-    <x:row r="61" ht="44" customHeight="1">
+    <x:row r="61" ht="66" hidden="0" customHeight="1">
       <x:c r="A61" s="9" t="str">
         <x:v>aegis-v1-030-malicious</x:v>
       </x:c>
@@ -5232,7 +5287,7 @@
       </x:c>
       <x:c r="X61" s="9" t="str"/>
     </x:row>
-    <x:row r="62" ht="44" customHeight="1">
+    <x:row r="62" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A62" s="9" t="str">
         <x:v>aegis-v1-031-benign</x:v>
       </x:c>
@@ -5306,7 +5361,7 @@
         <x:v>b9420aa42fa453be4f831fd4d328a001356acdb362c42d730f726dfa39844bd0</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="44" customHeight="1">
+    <x:row r="63" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A63" s="9" t="str">
         <x:v>aegis-v1-031-malicious</x:v>
       </x:c>
@@ -5380,7 +5435,7 @@
         <x:v>1c06c313354432daf62200b58f99e4c3c5eaa0135958225a06563858d1cc18ec</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="44" customHeight="1">
+    <x:row r="64" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A64" s="9" t="str">
         <x:v>aegis-v1-032-benign</x:v>
       </x:c>
@@ -5454,7 +5509,7 @@
         <x:v>aea09c2ee8ddaa38bf402b60e28bfcfc9e231a1e388cafb0dd30d5ff355d15c3</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="44" customHeight="1">
+    <x:row r="65" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A65" s="9" t="str">
         <x:v>aegis-v1-032-malicious</x:v>
       </x:c>
@@ -5535,7 +5590,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd82e3d8027754a30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2ba1b2d557f457d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5560,274 +5615,274 @@
         <x:v>Required</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="28" t="str">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="32" t="str">
         <x:v>sample_id</x:v>
       </x:c>
-      <x:c r="B2" s="28" t="str">
+      <x:c r="B2" s="32" t="str">
         <x:v>Unique benchmark row identifier.</x:v>
       </x:c>
-      <x:c r="C2" s="28" t="str">
+      <x:c r="C2" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="28" t="str">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="32" t="str">
         <x:v>split</x:v>
       </x:c>
-      <x:c r="B3" s="28" t="str">
+      <x:c r="B3" s="32" t="str">
         <x:v>Leakage-controlled train, validation, or test assignment.</x:v>
       </x:c>
-      <x:c r="C3" s="28" t="str">
+      <x:c r="C3" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="28" t="str">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="32" t="str">
         <x:v>group_id</x:v>
       </x:c>
-      <x:c r="B4" s="28" t="str">
+      <x:c r="B4" s="32" t="str">
         <x:v>Matched benign/adversarial pair identifier; groups do not cross splits.</x:v>
       </x:c>
-      <x:c r="C4" s="28" t="str">
+      <x:c r="C4" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="28" t="str">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="32" t="str">
         <x:v>label</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="str">
+      <x:c r="B5" s="32" t="str">
         <x:v>Human-readable binary decision.</x:v>
       </x:c>
-      <x:c r="C5" s="28" t="str">
+      <x:c r="C5" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="28" t="str">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="32" t="str">
         <x:v>label_id</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="str">
+      <x:c r="B6" s="32" t="str">
         <x:v>Machine-readable label: benign=0, malicious=1.</x:v>
       </x:c>
-      <x:c r="C6" s="28" t="str">
+      <x:c r="C6" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="28" t="str">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="32" t="str">
         <x:v>modality</x:v>
       </x:c>
-      <x:c r="B7" s="28" t="str">
+      <x:c r="B7" s="32" t="str">
         <x:v>text or image_text.</x:v>
       </x:c>
-      <x:c r="C7" s="28" t="str">
+      <x:c r="C7" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="28" t="str">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="32" t="str">
         <x:v>prompt_text</x:v>
       </x:c>
-      <x:c r="B8" s="28" t="str">
+      <x:c r="B8" s="32" t="str">
         <x:v>User-visible text prompt; harmful operational details are redacted.</x:v>
       </x:c>
-      <x:c r="C8" s="28" t="str">
+      <x:c r="C8" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="28" t="str">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="32" t="str">
         <x:v>image_path</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="str">
+      <x:c r="B9" s="32" t="str">
         <x:v>Relative generated PNG path; empty for text-only rows.</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="str">
+      <x:c r="C9" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="28" t="str">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="32" t="str">
         <x:v>harm_category</x:v>
       </x:c>
-      <x:c r="B10" s="28" t="str">
+      <x:c r="B10" s="32" t="str">
         <x:v>Requested policy harm, or none for benign rows.</x:v>
       </x:c>
-      <x:c r="C10" s="28" t="str">
+      <x:c r="C10" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="28" t="str">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="32" t="str">
         <x:v>attack_style</x:v>
       </x:c>
-      <x:c r="B11" s="28" t="str">
+      <x:c r="B11" s="32" t="str">
         <x:v>Observed adversarial mechanism, or none for benign rows.</x:v>
       </x:c>
-      <x:c r="C11" s="28" t="str">
+      <x:c r="C11" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="28" t="str">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="32" t="str">
         <x:v>paired_attack_style</x:v>
       </x:c>
-      <x:c r="B12" s="28" t="str">
+      <x:c r="B12" s="32" t="str">
         <x:v>Attack family represented by both rows in the matched pair.</x:v>
       </x:c>
-      <x:c r="C12" s="28" t="str">
+      <x:c r="C12" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="28" t="str">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="32" t="str">
         <x:v>scenario_theme</x:v>
       </x:c>
-      <x:c r="B13" s="28" t="str">
+      <x:c r="B13" s="32" t="str">
         <x:v>Benign topic used to construct the matched scenario.</x:v>
       </x:c>
-      <x:c r="C13" s="28" t="str">
+      <x:c r="C13" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="28" t="str">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="32" t="str">
         <x:v>obfuscation_type</x:v>
       </x:c>
-      <x:c r="B14" s="28" t="str">
+      <x:c r="B14" s="32" t="str">
         <x:v>Redaction/obfuscation marker.</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="str">
+      <x:c r="C14" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="28" t="str">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="32" t="str">
         <x:v>policy_rationale</x:v>
       </x:c>
-      <x:c r="B15" s="28" t="str">
+      <x:c r="B15" s="32" t="str">
         <x:v>One-sentence annotation justification.</x:v>
       </x:c>
-      <x:c r="C15" s="28" t="str">
+      <x:c r="C15" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="28" t="str">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="32" t="str">
         <x:v>annotation_method</x:v>
       </x:c>
-      <x:c r="B16" s="28" t="str">
+      <x:c r="B16" s="32" t="str">
         <x:v>How the label was authored and validated.</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="str">
+      <x:c r="C16" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="28" t="str">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="32" t="str">
         <x:v>annotation_confidence</x:v>
       </x:c>
-      <x:c r="B17" s="28" t="str">
+      <x:c r="B17" s="32" t="str">
         <x:v>Confidence from 0 to 1.</x:v>
       </x:c>
-      <x:c r="C17" s="28" t="str">
+      <x:c r="C17" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="28" t="str">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="32" t="str">
         <x:v>annotation_status</x:v>
       </x:c>
-      <x:c r="B18" s="28" t="str">
+      <x:c r="B18" s="32" t="str">
         <x:v>Synthetic annotation maturity marker.</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="str">
+      <x:c r="C18" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="28" t="str">
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="32" t="str">
         <x:v>pii_status</x:v>
       </x:c>
-      <x:c r="B19" s="28" t="str">
+      <x:c r="B19" s="32" t="str">
         <x:v>Personal-information screening outcome.</x:v>
       </x:c>
-      <x:c r="C19" s="28" t="str">
+      <x:c r="C19" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="28" t="str">
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="32" t="str">
         <x:v>content_safety</x:v>
       </x:c>
-      <x:c r="B20" s="28" t="str">
+      <x:c r="B20" s="32" t="str">
         <x:v>Safe-handling state of the sample.</x:v>
       </x:c>
-      <x:c r="C20" s="28" t="str">
+      <x:c r="C20" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="28" t="str">
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="32" t="str">
         <x:v>source</x:v>
       </x:c>
-      <x:c r="B21" s="28" t="str">
+      <x:c r="B21" s="32" t="str">
         <x:v>Dataset provenance identifier.</x:v>
       </x:c>
-      <x:c r="C21" s="28" t="str">
+      <x:c r="C21" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="28" t="str">
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="32" t="str">
         <x:v>license</x:v>
       </x:c>
-      <x:c r="B22" s="28" t="str">
+      <x:c r="B22" s="32" t="str">
         <x:v>Current usage/release status.</x:v>
       </x:c>
-      <x:c r="C22" s="28" t="str">
+      <x:c r="C22" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="28" t="str">
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="32" t="str">
         <x:v>benchmark_version</x:v>
       </x:c>
-      <x:c r="B23" s="28" t="str">
+      <x:c r="B23" s="32" t="str">
         <x:v>Semantic dataset version.</x:v>
       </x:c>
-      <x:c r="C23" s="28" t="str">
+      <x:c r="C23" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="28" t="str">
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="32" t="str">
         <x:v>prompt_sha256</x:v>
       </x:c>
-      <x:c r="B24" s="28" t="str">
+      <x:c r="B24" s="32" t="str">
         <x:v>SHA-256 of normalized prompt text.</x:v>
       </x:c>
-      <x:c r="C24" s="28" t="str">
+      <x:c r="C24" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="28" t="str">
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="32" t="str">
         <x:v>image_sha256</x:v>
       </x:c>
-      <x:c r="B25" s="28" t="str">
+      <x:c r="B25" s="32" t="str">
         <x:v>SHA-256 of image bytes, blank for text-only rows.</x:v>
       </x:c>
-      <x:c r="C25" s="28" t="str">
+      <x:c r="C25" s="32" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3761ff09f5994ace"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5077dc0664254139"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/deliverables/benchmark/benchmark.xlsx
+++ b/deliverables/benchmark/benchmark.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbbe9db14a5ff420f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="2" r:id="R4386ad4c396144cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="3" r:id="R477fb98c20744fff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R96ebad728366446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="2" r:id="R16337f064c984461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="3" r:id="R84bac05372aa4666"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -790,7 +790,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="31" t="str">
-        <x:v>This workbook documents a synthetic, safety-redacted dataset. It is not a performance report for the deployed LLaVA tuned-v3 detector; current live-system evidence is recorded under deliverables/runtime_validation/.</x:v>
+        <x:v>This workbook documents a synthetic, safety-redacted dataset. It is not detector-training data or a performance report for any maintained AEGIS target; runtime evidence is recorded under deliverables/runtime_validation/.</x:v>
       </x:c>
       <x:c r="B21" s="31"/>
       <x:c r="C21" s="31"/>
@@ -5590,7 +5590,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2ba1b2d557f457d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6284dc5766447a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5882,7 +5882,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5077dc0664254139"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c68a1b2a4a0416d"/>
   </x:tableParts>
 </x:worksheet>
 </file>